--- a/IVBVAR/Input/DATA_Monthly_2008_2025.xlsx
+++ b/IVBVAR/Input/DATA_Monthly_2008_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bancodelarepublica-my.sharepoint.com/personal/ojaulime_banrep_gov_co/Documents/Documents/Research/MP transmission in Colombia/Monetary-Policy-Shocks-and-Central-bank-information-in-Colombia/IVBVAR/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{1E7B483F-4085-46C9-BB4B-6E74D227E94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A1ABD6D-C908-4A33-B776-8F5A065F1618}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="8_{1E7B483F-4085-46C9-BB4B-6E74D227E94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96518712-692C-4FE9-8E6B-ADED5322FC12}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-1270" windowWidth="19420" windowHeight="11500" xr2:uid="{84727D96-C1F4-4C5D-A4E6-BED42547CEF0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{84727D96-C1F4-4C5D-A4E6-BED42547CEF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Fecha</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>WTI</t>
+  </si>
+  <si>
+    <t>Shockbloo</t>
   </si>
 </sst>
 </file>
@@ -505,13 +508,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8473D73C-976F-4322-83BA-3861F830F139}">
-  <dimension ref="A1:AE217"/>
+  <dimension ref="A1:AF217"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -600,13 +603,16 @@
         <v>15</v>
       </c>
       <c r="AD1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>39448</v>
       </c>
@@ -690,13 +696,17 @@
         <v>-1.635267E-2</v>
       </c>
       <c r="AD2">
+        <f>AB2+AC2</f>
+        <v>-0.04</v>
+      </c>
+      <c r="AE2">
         <v>3.2193769999999997E-2</v>
       </c>
-      <c r="AE2">
+      <c r="AF2">
         <v>-0.12919377000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>39479</v>
       </c>
@@ -786,13 +796,17 @@
         <v>8.1367750000000003E-2</v>
       </c>
       <c r="AD3">
+        <f t="shared" ref="AD3:AD66" si="1">AB3+AC3</f>
+        <v>0.16</v>
+      </c>
+      <c r="AE3">
         <v>7.1507870000000001E-2</v>
       </c>
-      <c r="AE3">
+      <c r="AF3">
         <v>4.2492130000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>39508</v>
       </c>
@@ -882,13 +896,17 @@
         <v>0.22795829000000001</v>
       </c>
       <c r="AD4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE4">
         <v>-3.7636080000000002E-2</v>
       </c>
-      <c r="AE4">
+      <c r="AF4">
         <v>-5.2363920000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>39539</v>
       </c>
@@ -978,13 +996,17 @@
         <v>0.25212187000000003</v>
       </c>
       <c r="AD5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE5">
         <v>-0.12609600000000001</v>
       </c>
-      <c r="AE5">
+      <c r="AF5">
         <v>4.4096000000000003E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>39569</v>
       </c>
@@ -1074,13 +1096,17 @@
         <v>-0.27712186999999999</v>
       </c>
       <c r="AD6">
+        <f t="shared" si="1"/>
+        <v>-4.9999999999999989E-2</v>
+      </c>
+      <c r="AE6">
         <v>-7.8555699999999992E-3</v>
       </c>
-      <c r="AE6">
+      <c r="AF6">
         <v>-7.0144429999999994E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>39600</v>
       </c>
@@ -1170,13 +1196,17 @@
         <v>-0.29847454000000001</v>
       </c>
       <c r="AD7">
+        <f t="shared" si="1"/>
+        <v>-0.1</v>
+      </c>
+      <c r="AE7">
         <v>-3.7725059999999998E-2</v>
       </c>
-      <c r="AE7">
+      <c r="AF7">
         <v>-4.0274940000000002E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>39630</v>
       </c>
@@ -1266,13 +1296,17 @@
         <v>0.29842929000000001</v>
       </c>
       <c r="AD8">
+        <f t="shared" si="1"/>
+        <v>0.13</v>
+      </c>
+      <c r="AE8">
         <v>0.1833275</v>
       </c>
-      <c r="AE8">
+      <c r="AF8">
         <v>-1.7327499999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>39661</v>
       </c>
@@ -1362,13 +1396,17 @@
         <v>-1.7735500000000001E-2</v>
       </c>
       <c r="AD9">
+        <f t="shared" si="1"/>
+        <v>-0.03</v>
+      </c>
+      <c r="AE9">
         <v>-4.55748E-3</v>
       </c>
-      <c r="AE9">
+      <c r="AF9">
         <v>-7.644252E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>39692</v>
       </c>
@@ -1458,13 +1496,17 @@
         <v>1.7780750000000001E-2</v>
       </c>
       <c r="AD10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE10">
         <v>-1.680301E-2</v>
       </c>
-      <c r="AE10">
+      <c r="AF10">
         <v>-5.319699E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>39722</v>
       </c>
@@ -1554,13 +1596,17 @@
         <v>-0.27084460999999999</v>
       </c>
       <c r="AD11">
+        <f t="shared" si="1"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AE11">
         <v>0.20942722999999999</v>
       </c>
-      <c r="AE11">
+      <c r="AF11">
         <v>-0.29042722999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>39753</v>
       </c>
@@ -1650,13 +1696,17 @@
         <v>-0.19792813000000001</v>
       </c>
       <c r="AD12">
+        <f t="shared" si="1"/>
+        <v>3.999999999999998E-2</v>
+      </c>
+      <c r="AE12">
         <v>-0.30901500999999998</v>
       </c>
-      <c r="AE12">
+      <c r="AF12">
         <v>0.25201500999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>39783</v>
       </c>
@@ -1746,13 +1796,17 @@
         <v>-3.5301199999999999E-3</v>
       </c>
       <c r="AD13">
+        <f t="shared" si="1"/>
+        <v>-0.38</v>
+      </c>
+      <c r="AE13">
         <v>-0.16842077</v>
       </c>
-      <c r="AE13">
+      <c r="AF13">
         <v>-0.12657922999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>39814</v>
       </c>
@@ -1842,13 +1896,17 @@
         <v>-0.15318797000000001</v>
       </c>
       <c r="AD14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE14">
         <v>-0.14125931</v>
       </c>
-      <c r="AE14">
+      <c r="AF14">
         <v>-0.30674068999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>39845</v>
       </c>
@@ -1938,13 +1996,17 @@
         <v>-0.25638283000000001</v>
       </c>
       <c r="AD15">
+        <f t="shared" si="1"/>
+        <v>-0.5</v>
+      </c>
+      <c r="AE15">
         <v>-0.32733971000000001</v>
       </c>
-      <c r="AE15">
+      <c r="AF15">
         <v>-0.74666029</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>39873</v>
       </c>
@@ -2034,13 +2096,17 @@
         <v>-5.9269199999999996E-3</v>
       </c>
       <c r="AD16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE16">
         <v>-0.61211327000000004</v>
       </c>
-      <c r="AE16">
+      <c r="AF16">
         <v>-0.39488673000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>39904</v>
       </c>
@@ -2130,13 +2196,17 @@
         <v>-2.4619499999999999E-2</v>
       </c>
       <c r="AD17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE17">
         <v>-0.65896052999999999</v>
       </c>
-      <c r="AE17">
+      <c r="AF17">
         <v>-0.36303946999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>39934</v>
       </c>
@@ -2226,13 +2296,17 @@
         <v>-4.5592000000000001E-4</v>
       </c>
       <c r="AD18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE18">
         <v>-0.69197914000000005</v>
       </c>
-      <c r="AE18">
+      <c r="AF18">
         <v>-0.31302086000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>39965</v>
       </c>
@@ -2322,13 +2396,17 @@
         <v>-0.23114971000000001</v>
       </c>
       <c r="AD19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE19">
         <v>-0.25120069</v>
       </c>
-      <c r="AE19">
+      <c r="AF19">
         <v>-0.27379931000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>39995</v>
       </c>
@@ -2418,13 +2496,17 @@
         <v>8.6624200000000005E-3</v>
       </c>
       <c r="AD20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE20">
         <v>2.3489429999999999E-2</v>
       </c>
-      <c r="AE20">
+      <c r="AF20">
         <v>-2.548943E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>40026</v>
       </c>
@@ -2514,13 +2596,17 @@
         <v>-1.003016E-2</v>
       </c>
       <c r="AD21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE21">
         <v>0.11863451</v>
       </c>
-      <c r="AE21">
+      <c r="AF21">
         <v>4.2365489999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>40057</v>
       </c>
@@ -2610,13 +2696,17 @@
         <v>-0.26914850000000001</v>
       </c>
       <c r="AD22">
+        <f t="shared" si="1"/>
+        <v>-0.5</v>
+      </c>
+      <c r="AE22">
         <v>-0.38558516999999998</v>
       </c>
-      <c r="AE22">
+      <c r="AF22">
         <v>-3.341483E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>40087</v>
       </c>
@@ -2706,13 +2796,17 @@
         <v>-9.1182999999999998E-4</v>
       </c>
       <c r="AD23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE23">
         <v>8.659348E-2</v>
       </c>
-      <c r="AE23">
+      <c r="AF23">
         <v>-0.10859348000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>40118</v>
       </c>
@@ -2802,13 +2896,17 @@
         <v>-0.31519606999999999</v>
       </c>
       <c r="AD24">
+        <f t="shared" si="1"/>
+        <v>-0.5</v>
+      </c>
+      <c r="AE24">
         <v>-0.29311102999999999</v>
       </c>
-      <c r="AE24">
+      <c r="AF24">
         <v>-0.20488897</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>40148</v>
       </c>
@@ -2898,13 +2996,17 @@
         <v>1.1853829999999999E-2</v>
       </c>
       <c r="AD25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE25">
         <v>0.10847347</v>
       </c>
-      <c r="AE25">
+      <c r="AF25">
         <v>9.8526530000000001E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>40179</v>
       </c>
@@ -2994,13 +3096,17 @@
         <v>5.9269199999999996E-3</v>
       </c>
       <c r="AD26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE26">
         <v>0.13674422</v>
       </c>
-      <c r="AE26">
+      <c r="AF26">
         <v>7.0255780000000004E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>40210</v>
       </c>
@@ -3090,13 +3196,17 @@
         <v>2.826683E-2</v>
       </c>
       <c r="AD27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE27">
         <v>4.4120220000000002E-2</v>
       </c>
-      <c r="AE27">
+      <c r="AF27">
         <v>6.7879780000000001E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>40238</v>
       </c>
@@ -3186,13 +3296,17 @@
         <v>0</v>
       </c>
       <c r="AD28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE28">
         <v>-4.0351999999999999E-4</v>
       </c>
-      <c r="AE28">
+      <c r="AF28">
         <v>7.6403520000000003E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>40269</v>
       </c>
@@ -3282,13 +3396,17 @@
         <v>-0.26185383000000001</v>
       </c>
       <c r="AD29">
+        <f t="shared" si="1"/>
+        <v>-0.5</v>
+      </c>
+      <c r="AE29">
         <v>-0.39427907000000001</v>
       </c>
-      <c r="AE29">
+      <c r="AF29">
         <v>-0.12372093000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>40299</v>
       </c>
@@ -3378,13 +3496,17 @@
         <v>-4.1032500000000001E-3</v>
       </c>
       <c r="AD30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE30">
         <v>-0.13344313999999999</v>
       </c>
-      <c r="AE30">
+      <c r="AF30">
         <v>8.5443140000000001E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>40330</v>
       </c>
@@ -3474,13 +3596,17 @@
         <v>-4.1032500000000001E-3</v>
       </c>
       <c r="AD31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE31">
         <v>9.4642200000000006E-3</v>
       </c>
-      <c r="AE31">
+      <c r="AF31">
         <v>-5.7464220000000003E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>40360</v>
       </c>
@@ -3570,13 +3696,17 @@
         <v>-3.1914199999999999E-3</v>
       </c>
       <c r="AD32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE32">
         <v>-0.17443388000000001</v>
       </c>
-      <c r="AE32">
+      <c r="AF32">
         <v>0.11943388000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>40391</v>
       </c>
@@ -3666,13 +3796,17 @@
         <v>0.13175988999999999</v>
       </c>
       <c r="AD33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE33">
         <v>-0.13762647</v>
       </c>
-      <c r="AE33">
+      <c r="AF33">
         <v>9.4626470000000004E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>40422</v>
       </c>
@@ -3762,13 +3896,17 @@
         <v>-7.8417650000000005E-2</v>
       </c>
       <c r="AD34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE34">
         <v>-0.10376365</v>
       </c>
-      <c r="AE34">
+      <c r="AF34">
         <v>4.1763649999999999E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>40452</v>
       </c>
@@ -3858,13 +3996,17 @@
         <v>1.8236699999999999E-3</v>
       </c>
       <c r="AD35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE35">
         <v>-8.1171220000000002E-2</v>
       </c>
-      <c r="AE35">
+      <c r="AF35">
         <v>2.9171220000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>40483</v>
       </c>
@@ -3954,13 +4096,17 @@
         <v>8.4344569999999994E-2</v>
       </c>
       <c r="AD36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE36">
         <v>-7.3863599999999998E-3</v>
       </c>
-      <c r="AE36">
+      <c r="AF36">
         <v>-4.0613639999999999E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>40513</v>
       </c>
@@ -4050,13 +4196,17 @@
         <v>-6.8387500000000002E-3</v>
       </c>
       <c r="AD37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE37">
         <v>2.7499E-3</v>
       </c>
-      <c r="AE37">
+      <c r="AF37">
         <v>-6.9749900000000004E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>40544</v>
       </c>
@@ -4146,13 +4296,17 @@
         <v>5.9269199999999996E-3</v>
       </c>
       <c r="AD38">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE38">
         <v>2.1859340000000001E-2</v>
       </c>
-      <c r="AE38">
+      <c r="AF38">
         <v>-8.5859340000000006E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>40575</v>
       </c>
@@ -4242,13 +4396,17 @@
         <v>0.13183875</v>
       </c>
       <c r="AD39">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="AE39">
         <v>-0.10696693</v>
       </c>
-      <c r="AE39">
+      <c r="AF39">
         <v>0.27196693</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>40603</v>
       </c>
@@ -4338,13 +4496,17 @@
         <v>0.10486081</v>
       </c>
       <c r="AD40">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE40">
         <v>6.5363619999999997E-2</v>
       </c>
-      <c r="AE40">
+      <c r="AF40">
         <v>8.3636379999999996E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40634</v>
       </c>
@@ -4434,13 +4596,17 @@
         <v>-9.1182999999999998E-4</v>
       </c>
       <c r="AD41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE41">
         <v>6.8974149999999998E-2</v>
       </c>
-      <c r="AE41">
+      <c r="AF41">
         <v>-1.8974149999999999E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40664</v>
       </c>
@@ -4530,13 +4696,17 @@
         <v>1.276566E-2</v>
       </c>
       <c r="AD42">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE42">
         <v>-7.401576E-2</v>
       </c>
-      <c r="AE42">
+      <c r="AF42">
         <v>0.15101576</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>40695</v>
       </c>
@@ -4626,13 +4796,17 @@
         <v>9.1182999999999998E-4</v>
       </c>
       <c r="AD43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE43">
         <v>8.6952420000000002E-2</v>
       </c>
-      <c r="AE43">
+      <c r="AF43">
         <v>3.1047580000000002E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>40725</v>
       </c>
@@ -4722,13 +4896,17 @@
         <v>-1.8236699999999999E-3</v>
       </c>
       <c r="AD44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE44">
         <v>-2.872106E-2</v>
       </c>
-      <c r="AE44">
+      <c r="AF44">
         <v>7.8721059999999995E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>40756</v>
       </c>
@@ -4818,13 +4996,17 @@
         <v>-0.22302205999999999</v>
       </c>
       <c r="AD45">
+        <f t="shared" si="1"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE45">
         <v>-7.738979E-2</v>
       </c>
-      <c r="AE45">
+      <c r="AF45">
         <v>-8.2610210000000003E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>40787</v>
       </c>
@@ -4914,13 +5096,17 @@
         <v>-6.3828299999999999E-3</v>
       </c>
       <c r="AD46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE46">
         <v>0.15082087999999999</v>
       </c>
-      <c r="AE46">
+      <c r="AF46">
         <v>-0.22582088</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>40817</v>
       </c>
@@ -5010,13 +5196,17 @@
         <v>-3.6473299999999998E-3</v>
       </c>
       <c r="AD47">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE47">
         <v>2.3002890000000002E-2</v>
       </c>
-      <c r="AE47">
+      <c r="AF47">
         <v>-0.13000289000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>40848</v>
       </c>
@@ -5106,13 +5296,17 @@
         <v>-6.3828299999999999E-3</v>
       </c>
       <c r="AD48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE48">
         <v>-0.12156836</v>
       </c>
-      <c r="AE48">
+      <c r="AF48">
         <v>0.23256836</v>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>40878</v>
       </c>
@@ -5202,13 +5396,17 @@
         <v>4.5592000000000001E-4</v>
       </c>
       <c r="AD49">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE49">
         <v>4.0924799999999999E-3</v>
       </c>
-      <c r="AE49">
+      <c r="AF49">
         <v>-7.5092480000000003E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>40909</v>
       </c>
@@ -5298,13 +5496,17 @@
         <v>0.13092692</v>
       </c>
       <c r="AD50">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="AE50">
         <v>-6.9510000000000004E-4</v>
       </c>
-      <c r="AE50">
+      <c r="AF50">
         <v>0.2106951</v>
       </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>40940</v>
       </c>
@@ -5394,13 +5596,17 @@
         <v>2.2795799999999998E-3</v>
       </c>
       <c r="AD51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE51">
         <v>0.14323707999999999</v>
       </c>
-      <c r="AE51">
+      <c r="AF51">
         <v>2.2762919999999999E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>40969</v>
       </c>
@@ -5490,13 +5696,17 @@
         <v>-5.0150799999999999E-3</v>
       </c>
       <c r="AD52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE52">
         <v>-8.2164210000000001E-2</v>
       </c>
-      <c r="AE52">
+      <c r="AF52">
         <v>7.4164209999999994E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>41000</v>
       </c>
@@ -5586,13 +5796,17 @@
         <v>-3.6473299999999998E-3</v>
       </c>
       <c r="AD53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE53">
         <v>-0.14462346000000001</v>
       </c>
-      <c r="AE53">
+      <c r="AF53">
         <v>0.13162346</v>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>41030</v>
       </c>
@@ -5682,13 +5896,17 @@
         <v>-0.13951047</v>
       </c>
       <c r="AD54">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE54">
         <v>-6.5997249999999993E-2</v>
       </c>
-      <c r="AE54">
+      <c r="AF54">
         <v>4.5997250000000003E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>41061</v>
       </c>
@@ -5778,13 +5996,17 @@
         <v>4.5592000000000001E-4</v>
       </c>
       <c r="AD55">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE55">
         <v>-0.18032713</v>
       </c>
-      <c r="AE55">
+      <c r="AF55">
         <v>0.13332712999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>41091</v>
       </c>
@@ -5874,13 +6096,17 @@
         <v>-0.12955917</v>
       </c>
       <c r="AD56">
+        <f t="shared" si="1"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE56">
         <v>-0.17074835999999999</v>
       </c>
-      <c r="AE56">
+      <c r="AF56">
         <v>-0.19025164</v>
       </c>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>41122</v>
       </c>
@@ -5970,13 +6196,17 @@
         <v>9.1182999999999998E-4</v>
       </c>
       <c r="AD57">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE57">
         <v>-6.1018429999999999E-2</v>
       </c>
-      <c r="AE57">
+      <c r="AF57">
         <v>-2.8981570000000002E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>41153</v>
       </c>
@@ -6066,13 +6296,17 @@
         <v>-9.4830650000000002E-2</v>
       </c>
       <c r="AD58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE58">
         <v>5.9945520000000002E-2</v>
       </c>
-      <c r="AE58">
+      <c r="AF58">
         <v>8.4054480000000001E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>41183</v>
       </c>
@@ -6162,13 +6396,17 @@
         <v>3.1914199999999999E-3</v>
       </c>
       <c r="AD59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE59">
         <v>-1.545011E-2</v>
       </c>
-      <c r="AE59">
+      <c r="AF59">
         <v>3.9450109999999997E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>41214</v>
       </c>
@@ -6258,13 +6496,17 @@
         <v>-0.1911079</v>
       </c>
       <c r="AD60">
+        <f t="shared" si="1"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE60">
         <v>-7.0666039999999999E-2</v>
       </c>
-      <c r="AE60">
+      <c r="AF60">
         <v>-0.16033396</v>
       </c>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>41244</v>
       </c>
@@ -6354,13 +6596,17 @@
         <v>-0.12363225</v>
       </c>
       <c r="AD61">
+        <f t="shared" si="1"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE61">
         <v>-0.11725770000000001</v>
       </c>
-      <c r="AE61">
+      <c r="AF61">
         <v>3.5257700000000003E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>41275</v>
       </c>
@@ -6450,13 +6696,17 @@
         <v>1.8236699999999999E-3</v>
       </c>
       <c r="AD62">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE62">
         <v>-9.1395399999999998E-3</v>
       </c>
-      <c r="AE62">
+      <c r="AF62">
         <v>4.0139540000000001E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>41306</v>
       </c>
@@ -6546,13 +6796,17 @@
         <v>7.9329479999999994E-2</v>
       </c>
       <c r="AD63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE63">
         <v>-3.3550919999999998E-2</v>
       </c>
-      <c r="AE63">
+      <c r="AF63">
         <v>1.8550919999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>41334</v>
       </c>
@@ -6642,13 +6896,17 @@
         <v>-0.19566707</v>
       </c>
       <c r="AD64">
+        <f t="shared" si="1"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE64">
         <v>-0.20136246999999999</v>
       </c>
-      <c r="AE64">
+      <c r="AF64">
         <v>-6.3637529999999998E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>41365</v>
       </c>
@@ -6738,13 +6996,17 @@
         <v>6.7475649999999998E-2</v>
       </c>
       <c r="AD65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE65">
         <v>9.2549439999999997E-2</v>
       </c>
-      <c r="AE65">
+      <c r="AF65">
         <v>4.1450559999999997E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>41395</v>
       </c>
@@ -6797,7 +7059,7 @@
         <v>4.2950135301065799</v>
       </c>
       <c r="R66">
-        <f t="shared" ref="R66:R129" si="1">Q66-G66</f>
+        <f t="shared" ref="R66:R129" si="2">Q66-G66</f>
         <v>-7.1896840321020505E-2</v>
       </c>
       <c r="S66">
@@ -6834,13 +7096,17 @@
         <v>9.6198400000000003E-2</v>
       </c>
       <c r="AD66">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE66">
         <v>-8.9867939999999993E-2</v>
       </c>
-      <c r="AE66">
+      <c r="AF66">
         <v>0.10686793999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>41426</v>
       </c>
@@ -6893,7 +7159,7 @@
         <v>4.3164661774317103</v>
       </c>
       <c r="R67">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.4242349309763682E-2</v>
       </c>
       <c r="S67">
@@ -6930,13 +7196,17 @@
         <v>0.11717056000000001</v>
       </c>
       <c r="AD67">
+        <f t="shared" ref="AD67:AD130" si="3">AB67+AC67</f>
+        <v>0</v>
+      </c>
+      <c r="AE67">
         <v>2.8595599999999999E-2</v>
       </c>
-      <c r="AE67">
+      <c r="AF67">
         <v>-1.5956E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>41456</v>
       </c>
@@ -6989,7 +7259,7 @@
         <v>4.2989947346681801</v>
       </c>
       <c r="R68">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.4201774672960852E-2</v>
       </c>
       <c r="S68">
@@ -7026,13 +7296,17 @@
         <v>9.2551069999999999E-2</v>
       </c>
       <c r="AD68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE68">
         <v>2.2833119999999998E-2</v>
       </c>
-      <c r="AE68">
+      <c r="AF68">
         <v>-2.6833119999999999E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>41487</v>
       </c>
@@ -7085,7 +7359,7 @@
         <v>4.2877513940814298</v>
       </c>
       <c r="R69">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.8566440248519562E-2</v>
       </c>
       <c r="S69">
@@ -7122,13 +7396,17 @@
         <v>-8.6168229999999998E-2</v>
       </c>
       <c r="AD69">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE69">
         <v>-2.328908E-2</v>
       </c>
-      <c r="AE69">
+      <c r="AF69">
         <v>7.2890799999999999E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>41518</v>
       </c>
@@ -7181,7 +7459,7 @@
         <v>4.2934982852890897</v>
       </c>
       <c r="R70">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.718735192019178E-2</v>
       </c>
       <c r="S70">
@@ -7218,13 +7496,17 @@
         <v>0</v>
       </c>
       <c r="AD70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE70">
         <v>8.2683400000000004E-2</v>
       </c>
-      <c r="AE70">
+      <c r="AF70">
         <v>-7.8683400000000001E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>41548</v>
       </c>
@@ -7277,7 +7559,7 @@
         <v>4.30502669316789</v>
       </c>
       <c r="R71">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.578681819280586E-2</v>
       </c>
       <c r="S71">
@@ -7314,13 +7596,17 @@
         <v>1.36775E-3</v>
       </c>
       <c r="AD71">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE71">
         <v>5.2251760000000001E-2</v>
       </c>
-      <c r="AE71">
+      <c r="AF71">
         <v>-5.3251760000000002E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>41579</v>
       </c>
@@ -7373,7 +7659,7 @@
         <v>4.3029666510014399</v>
       </c>
       <c r="R72">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.7725306379161196E-2</v>
       </c>
       <c r="S72">
@@ -7410,13 +7696,17 @@
         <v>0</v>
       </c>
       <c r="AD72">
-        <v>1.0999999999999999E-2</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AE72">
         <v>1.0999999999999999E-2</v>
       </c>
+      <c r="AF72">
+        <v>1.0999999999999999E-2</v>
+      </c>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>41609</v>
       </c>
@@ -7469,7 +7759,7 @@
         <v>4.3319973594067003</v>
       </c>
       <c r="R73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.128058186549378E-2</v>
       </c>
       <c r="S73">
@@ -7506,13 +7796,17 @@
         <v>1.8236699999999999E-3</v>
       </c>
       <c r="AD73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE73">
         <v>0.15738816</v>
       </c>
-      <c r="AE73">
+      <c r="AF73">
         <v>-0.14338815999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>41640</v>
       </c>
@@ -7565,7 +7859,7 @@
         <v>4.3169618899654001</v>
       </c>
       <c r="R74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.7017645687070804E-2</v>
       </c>
       <c r="S74">
@@ -7602,13 +7896,17 @@
         <v>3.1914199999999999E-3</v>
       </c>
       <c r="AD74">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE74">
         <v>5.8454020000000002E-2</v>
       </c>
-      <c r="AE74">
+      <c r="AF74">
         <v>-7.945402E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>41671</v>
       </c>
@@ -7661,7 +7959,7 @@
         <v>4.29886743828113</v>
       </c>
       <c r="R75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.5954595499903697E-2</v>
       </c>
       <c r="S75">
@@ -7698,13 +7996,17 @@
         <v>-9.1182999999999998E-4</v>
       </c>
       <c r="AD75">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE75">
         <v>9.3548859999999998E-2</v>
       </c>
-      <c r="AE75">
+      <c r="AF75">
         <v>-9.8548860000000002E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>41699</v>
       </c>
@@ -7757,7 +8059,7 @@
         <v>4.3163020432083998</v>
       </c>
       <c r="R76">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.0707347646683516E-2</v>
       </c>
       <c r="S76">
@@ -7794,13 +8096,17 @@
         <v>0</v>
       </c>
       <c r="AD76">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE76">
         <v>-0.14317668</v>
       </c>
-      <c r="AE76">
+      <c r="AF76">
         <v>0.19117667999999999</v>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>41730</v>
       </c>
@@ -7853,7 +8159,7 @@
         <v>4.3186373259220803</v>
       </c>
       <c r="R77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.1882005441404218E-2</v>
       </c>
       <c r="S77">
@@ -7890,13 +8196,17 @@
         <v>0.12272042</v>
       </c>
       <c r="AD77">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="AE77">
         <v>0.12409486</v>
       </c>
-      <c r="AE77">
+      <c r="AF77">
         <v>0.13090514</v>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>41760</v>
       </c>
@@ -7949,7 +8259,7 @@
         <v>4.33417127578132</v>
       </c>
       <c r="R78">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.1584484383060634E-2</v>
       </c>
       <c r="S78">
@@ -7986,13 +8296,17 @@
         <v>8.2065000000000003E-3</v>
       </c>
       <c r="AD78">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE78">
         <v>-9.7256949999999995E-2</v>
       </c>
-      <c r="AE78">
+      <c r="AF78">
         <v>0.11125694999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>41791</v>
       </c>
@@ -8045,7 +8359,7 @@
         <v>4.3546448693828701</v>
       </c>
       <c r="R79">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-4.3694314339639106E-2</v>
       </c>
       <c r="S79">
@@ -8082,13 +8396,17 @@
         <v>-3.6473299999999998E-3</v>
       </c>
       <c r="AD79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE79">
         <v>-1.1258580000000001E-2</v>
       </c>
-      <c r="AE79">
+      <c r="AF79">
         <v>-2.5741420000000001E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>41821</v>
       </c>
@@ -8141,7 +8459,7 @@
         <v>4.3439264992389699</v>
       </c>
       <c r="R80">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.7869636347085418E-2</v>
       </c>
       <c r="S80">
@@ -8178,13 +8496,17 @@
         <v>7.75058E-3</v>
       </c>
       <c r="AD80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE80">
         <v>6.0890279999999998E-2</v>
       </c>
-      <c r="AE80">
+      <c r="AF80">
         <v>4.5109719999999999E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>41852</v>
       </c>
@@ -8237,7 +8559,7 @@
         <v>4.3333199133490696</v>
       </c>
       <c r="R81">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.2772341212917091E-2</v>
       </c>
       <c r="S81">
@@ -8274,13 +8596,17 @@
         <v>-2.2795799999999998E-3</v>
       </c>
       <c r="AD81">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE81">
         <v>3.3023730000000001E-2</v>
       </c>
-      <c r="AE81">
+      <c r="AF81">
         <v>8.7976269999999995E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>41883</v>
       </c>
@@ -8333,7 +8659,7 @@
         <v>4.3545329263061996</v>
       </c>
       <c r="R82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.4380951934949628E-2</v>
       </c>
       <c r="S82">
@@ -8370,13 +8696,17 @@
         <v>4.1032500000000001E-3</v>
       </c>
       <c r="AD82">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE82">
         <v>1.6300000000000001E-6</v>
       </c>
-      <c r="AE82">
+      <c r="AF82">
         <v>4.9983700000000002E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>41913</v>
       </c>
@@ -8429,7 +8759,7 @@
         <v>4.3564880528157603</v>
       </c>
       <c r="R83">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.6767616582907188E-2</v>
       </c>
       <c r="S83">
@@ -8466,13 +8796,17 @@
         <v>-1.504525E-2</v>
       </c>
       <c r="AD83">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE83">
         <v>-4.589319E-2</v>
       </c>
-      <c r="AE83">
+      <c r="AF83">
         <v>4.6893190000000001E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>41944</v>
       </c>
@@ -8525,7 +8859,7 @@
         <v>4.3518006839904304</v>
       </c>
       <c r="R84">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.4808859822427678E-2</v>
       </c>
       <c r="S84">
@@ -8562,13 +8896,17 @@
         <v>-9.1182999999999998E-4</v>
       </c>
       <c r="AD84">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE84">
         <v>9.1891730000000005E-2</v>
       </c>
-      <c r="AE84">
+      <c r="AF84">
         <v>-8.7891730000000001E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>41974</v>
       </c>
@@ -8621,7 +8959,7 @@
         <v>4.3935848990558597</v>
       </c>
       <c r="R85">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-2.5630395745457335E-2</v>
       </c>
       <c r="S85">
@@ -8658,13 +8996,17 @@
         <v>-3.1914159999999997E-2</v>
       </c>
       <c r="AD85">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE85">
         <v>-0.36722569999999999</v>
       </c>
-      <c r="AE85">
+      <c r="AF85">
         <v>0.36922569999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>42005</v>
       </c>
@@ -8717,7 +9059,7 @@
         <v>4.3556313818830503</v>
       </c>
       <c r="R86">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.5758165446786698E-2</v>
       </c>
       <c r="S86">
@@ -8754,13 +9096,17 @@
         <v>1.8236699999999999E-3</v>
       </c>
       <c r="AD86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE86">
         <v>-0.11991789</v>
       </c>
-      <c r="AE86">
+      <c r="AF86">
         <v>0.11991789</v>
       </c>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>42036</v>
       </c>
@@ -8813,7 +9159,7 @@
         <v>4.3471707978308496</v>
       </c>
       <c r="R87">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.0284446948477139E-2</v>
       </c>
       <c r="S87">
@@ -8850,13 +9196,17 @@
         <v>-4.5592000000000001E-4</v>
       </c>
       <c r="AD87">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE87">
         <v>-4.361922E-2</v>
       </c>
-      <c r="AE87">
+      <c r="AF87">
         <v>4.5619220000000002E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>42064</v>
       </c>
@@ -8909,7 +9259,7 @@
         <v>4.3522411976684801</v>
       </c>
       <c r="R88">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.9265467427940273E-2</v>
       </c>
       <c r="S88">
@@ -8946,13 +9296,17 @@
         <v>-2.7355000000000001E-3</v>
       </c>
       <c r="AD88">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE88">
         <v>5.0272589999999999E-2</v>
       </c>
-      <c r="AE88">
+      <c r="AF88">
         <v>-5.127259E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>42095</v>
       </c>
@@ -9005,7 +9359,7 @@
         <v>4.3589147182412997</v>
       </c>
       <c r="R89">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.6823986098361274E-2</v>
       </c>
       <c r="S89">
@@ -9042,13 +9396,17 @@
         <v>1.230975E-2</v>
       </c>
       <c r="AD89">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE89">
         <v>-0.11839599000000001</v>
       </c>
-      <c r="AE89">
+      <c r="AF89">
         <v>0.10639599</v>
       </c>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>42125</v>
       </c>
@@ -9101,7 +9459,7 @@
         <v>4.3649291374712504</v>
       </c>
       <c r="R90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.3900182828663397E-2</v>
       </c>
       <c r="S90">
@@ -9138,13 +9496,17 @@
         <v>-1.0942E-2</v>
       </c>
       <c r="AD90">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE90">
         <v>3.383282E-2</v>
       </c>
-      <c r="AE90">
+      <c r="AF90">
         <v>-4.183282E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>42156</v>
       </c>
@@ -9197,7 +9559,7 @@
         <v>4.3963301487640898</v>
       </c>
       <c r="R91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-4.5211347001495206E-2</v>
       </c>
       <c r="S91">
@@ -9234,13 +9596,17 @@
         <v>-3.1914199999999999E-3</v>
       </c>
       <c r="AD91">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE91">
         <v>9.7541550000000005E-2</v>
       </c>
-      <c r="AE91">
+      <c r="AF91">
         <v>-0.10854155</v>
       </c>
     </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>42186</v>
       </c>
@@ -9293,7 +9659,7 @@
         <v>4.3771674929620001</v>
       </c>
       <c r="R92">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.8249276389717117E-2</v>
       </c>
       <c r="S92">
@@ -9330,13 +9696,17 @@
         <v>1.504525E-2</v>
       </c>
       <c r="AD92">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE92">
         <v>0.10641584</v>
       </c>
-      <c r="AE92">
+      <c r="AF92">
         <v>-0.14041583999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>42217</v>
       </c>
@@ -9389,7 +9759,7 @@
         <v>4.3729058043673001</v>
       </c>
       <c r="R93">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.9522653815518041E-2</v>
       </c>
       <c r="S93">
@@ -9426,13 +9796,17 @@
         <v>-1.36775E-3</v>
       </c>
       <c r="AD93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE93">
         <v>0.25540633000000001</v>
       </c>
-      <c r="AE93">
+      <c r="AF93">
         <v>-0.37040633000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>42248</v>
       </c>
@@ -9485,7 +9859,7 @@
         <v>4.3902597061264297</v>
       </c>
       <c r="R94">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.0721952961197765E-2</v>
       </c>
       <c r="S94">
@@ -9522,13 +9896,17 @@
         <v>0.12864733</v>
       </c>
       <c r="AD94">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="AE94">
         <v>0.15727141</v>
       </c>
-      <c r="AE94">
+      <c r="AF94">
         <v>-1.8271409999999998E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>42278</v>
       </c>
@@ -9581,7 +9959,7 @@
         <v>4.3974589888408104</v>
       </c>
       <c r="R95">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.3103826638305947E-2</v>
       </c>
       <c r="S95">
@@ -9618,13 +9996,17 @@
         <v>0.13730975000000001</v>
       </c>
       <c r="AD95">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="AE95">
         <v>6.9434309999999999E-2</v>
       </c>
-      <c r="AE95">
+      <c r="AF95">
         <v>6.6565689999999997E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>42309</v>
       </c>
@@ -9677,7 +10059,7 @@
         <v>4.3875398523507796</v>
       </c>
       <c r="R96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-9.1098388326908974E-2</v>
       </c>
       <c r="S96">
@@ -9714,13 +10096,17 @@
         <v>-0.12636775</v>
       </c>
       <c r="AD96">
+        <f t="shared" si="3"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE96">
         <v>-0.2414597</v>
       </c>
-      <c r="AE96">
+      <c r="AF96">
         <v>9.7459699999999996E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>42339</v>
       </c>
@@ -9773,7 +10159,7 @@
         <v>4.4209439821105398</v>
       </c>
       <c r="R97">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.3776756990884031E-2</v>
       </c>
       <c r="S97">
@@ -9810,13 +10196,17 @@
         <v>1.36775E-3</v>
       </c>
       <c r="AD97">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE97">
         <v>2.5573539999999999E-2</v>
       </c>
-      <c r="AE97">
+      <c r="AF97">
         <v>-0.10857354</v>
       </c>
     </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>42370</v>
       </c>
@@ -9869,7 +10259,7 @@
         <v>4.4081718954878104</v>
       </c>
       <c r="R98">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.5102640488184278E-2</v>
       </c>
       <c r="S98">
@@ -9906,13 +10296,17 @@
         <v>-4.5592000000000001E-4</v>
       </c>
       <c r="AD98">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE98">
         <v>-8.4253930000000005E-2</v>
       </c>
-      <c r="AE98">
+      <c r="AF98">
         <v>-7.4607000000000004E-4</v>
       </c>
     </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>42401</v>
       </c>
@@ -9965,7 +10359,7 @@
         <v>4.4062761856462904</v>
       </c>
       <c r="R99">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-9.42647260364744E-2</v>
       </c>
       <c r="S99">
@@ -10002,13 +10396,17 @@
         <v>-2.2795799999999998E-3</v>
       </c>
       <c r="AD99">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE99">
         <v>-5.1679740000000002E-2</v>
       </c>
-      <c r="AE99">
+      <c r="AF99">
         <v>-3.1320260000000003E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>42430</v>
       </c>
@@ -10061,7 +10459,7 @@
         <v>4.4154967882598601</v>
       </c>
       <c r="R100">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-9.2617620476896256E-2</v>
       </c>
       <c r="S100">
@@ -10098,13 +10496,17 @@
         <v>4.1032500000000001E-3</v>
       </c>
       <c r="AD100">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE100">
         <v>-2.428841E-2</v>
       </c>
-      <c r="AE100">
+      <c r="AF100">
         <v>7.0288409999999996E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>42461</v>
       </c>
@@ -10157,7 +10559,7 @@
         <v>4.4212639525561501</v>
       </c>
       <c r="R101">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-9.0686774267735082E-2</v>
       </c>
       <c r="S101">
@@ -10194,13 +10596,17 @@
         <v>0.13001508000000001</v>
       </c>
       <c r="AD101">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="AE101">
         <v>0.10097945999999999</v>
       </c>
-      <c r="AE101">
+      <c r="AF101">
         <v>0.10202054000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>42491</v>
       </c>
@@ -10253,7 +10659,7 @@
         <v>4.4356434776663702</v>
       </c>
       <c r="R102">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.195966219160411E-2</v>
       </c>
       <c r="S102">
@@ -10290,13 +10696,17 @@
         <v>2.2795799999999998E-3</v>
       </c>
       <c r="AD102">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE102">
         <v>4.4316590000000003E-2</v>
       </c>
-      <c r="AE102">
+      <c r="AF102">
         <v>-8.831659E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>42522</v>
       </c>
@@ -10349,7 +10759,7 @@
         <v>4.4577464785644096</v>
       </c>
       <c r="R103">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.6341222066271577E-2</v>
       </c>
       <c r="S103">
@@ -10386,13 +10796,17 @@
         <v>-9.1182999999999998E-4</v>
       </c>
       <c r="AD103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE103">
         <v>-2.5905020000000001E-2</v>
       </c>
-      <c r="AE103">
+      <c r="AF103">
         <v>1.7905020000000001E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>42552</v>
       </c>
@@ -10445,7 +10859,7 @@
         <v>4.4477151718854202</v>
       </c>
       <c r="R104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.3528487892360559E-2</v>
       </c>
       <c r="S104">
@@ -10482,13 +10896,17 @@
         <v>-2.826683E-2</v>
       </c>
       <c r="AD104">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE104">
         <v>5.4202010000000002E-2</v>
       </c>
-      <c r="AE104">
+      <c r="AF104">
         <v>2.4797989999999999E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>42583</v>
       </c>
@@ -10541,7 +10959,7 @@
         <v>4.43572830250897</v>
       </c>
       <c r="R105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-9.4632218397201484E-2</v>
       </c>
       <c r="S105">
@@ -10578,13 +10996,17 @@
         <v>-6.8387500000000002E-3</v>
       </c>
       <c r="AD105">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE105">
         <v>-4.112532E-2</v>
       </c>
-      <c r="AE105">
+      <c r="AF105">
         <v>-5.0874679999999999E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>42614</v>
       </c>
@@ -10637,7 +11059,7 @@
         <v>4.4437048727669897</v>
       </c>
       <c r="R106">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.7563697280501174E-2</v>
       </c>
       <c r="S106">
@@ -10674,13 +11096,17 @@
         <v>-1.8236699999999999E-3</v>
       </c>
       <c r="AD106">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE106">
         <v>5.45589E-2</v>
       </c>
-      <c r="AE106">
+      <c r="AF106">
         <v>-5.35589E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>42644</v>
       </c>
@@ -10733,7 +11159,7 @@
         <v>4.4549771214330596</v>
       </c>
       <c r="R107">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.8452312739837105E-2</v>
       </c>
       <c r="S107">
@@ -10770,13 +11196,17 @@
         <v>-9.1182999999999998E-4</v>
       </c>
       <c r="AD107">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE107">
         <v>-2.628277E-2</v>
       </c>
-      <c r="AE107">
+      <c r="AF107">
         <v>3.2282770000000002E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>42675</v>
       </c>
@@ -10829,7 +11259,7 @@
         <v>4.4553067273085203</v>
       </c>
       <c r="R108">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.1314980315188023E-2</v>
       </c>
       <c r="S108">
@@ -10866,13 +11296,17 @@
         <v>2.2795799999999998E-3</v>
       </c>
       <c r="AD108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE108">
         <v>3.9512970000000001E-2</v>
       </c>
-      <c r="AE108">
+      <c r="AF108">
         <v>-3.751297E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>42705</v>
       </c>
@@ -10925,7 +11359,7 @@
         <v>4.4885253296635703</v>
       </c>
       <c r="R109">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.2094035150247464E-2</v>
       </c>
       <c r="S109">
@@ -10962,13 +11396,17 @@
         <v>-0.12727958</v>
       </c>
       <c r="AD109">
+        <f t="shared" si="3"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE109">
         <v>-9.5227919999999994E-2</v>
       </c>
-      <c r="AE109">
+      <c r="AF109">
         <v>-0.11477208</v>
       </c>
     </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>42736</v>
       </c>
@@ -11021,7 +11459,7 @@
         <v>4.4814233176885097</v>
       </c>
       <c r="R110">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.5108119759190508E-2</v>
       </c>
       <c r="S110">
@@ -11058,13 +11496,17 @@
         <v>0.13229467</v>
       </c>
       <c r="AD110">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="AE110">
         <v>0.13307658999999999</v>
       </c>
-      <c r="AE110">
+      <c r="AF110">
         <v>3.4923410000000002E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>42767</v>
       </c>
@@ -11117,7 +11559,7 @@
         <v>4.4639712389859598</v>
       </c>
       <c r="R111">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.704658555999778E-2</v>
       </c>
       <c r="S111">
@@ -11154,13 +11596,17 @@
         <v>-0.12819142</v>
       </c>
       <c r="AD111">
+        <f t="shared" si="3"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE111">
         <v>-8.0262260000000002E-2</v>
       </c>
-      <c r="AE111">
+      <c r="AF111">
         <v>-6.8737740000000006E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>42795</v>
       </c>
@@ -11213,7 +11659,7 @@
         <v>4.4716775517684599</v>
       </c>
       <c r="R112">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.2294805356193379E-2</v>
       </c>
       <c r="S112">
@@ -11250,13 +11696,17 @@
         <v>-4.5592000000000001E-4</v>
       </c>
       <c r="AD112">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE112">
         <v>4.6907400000000002E-2</v>
       </c>
-      <c r="AE112">
+      <c r="AF112">
         <v>5.3092599999999997E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>42826</v>
       </c>
@@ -11309,7 +11759,7 @@
         <v>4.4760974445414803</v>
       </c>
       <c r="R113">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.1446286905268117E-2</v>
       </c>
       <c r="S113">
@@ -11346,13 +11796,17 @@
         <v>-0.13092692</v>
       </c>
       <c r="AD113">
+        <f t="shared" si="3"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE113">
         <v>-2.8875060000000001E-2</v>
       </c>
-      <c r="AE113">
+      <c r="AF113">
         <v>-8.1249400000000006E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>42856</v>
       </c>
@@ -11405,7 +11859,7 @@
         <v>4.4871197847757101</v>
       </c>
       <c r="R114">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.3201144148135278E-2</v>
       </c>
       <c r="S114">
@@ -11442,13 +11896,17 @@
         <v>-4.5592000000000001E-4</v>
       </c>
       <c r="AD114">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE114">
         <v>7.8727649999999996E-2</v>
       </c>
-      <c r="AE114">
+      <c r="AF114">
         <v>2.0272350000000001E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>42887</v>
       </c>
@@ -11501,7 +11959,7 @@
         <v>4.5031796372474</v>
       </c>
       <c r="R115">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.0030686021017132E-2</v>
       </c>
       <c r="S115">
@@ -11538,13 +11996,17 @@
         <v>-1.0942E-2</v>
       </c>
       <c r="AD115">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE115">
         <v>-7.7341499999999994E-2</v>
       </c>
-      <c r="AE115">
+      <c r="AF115">
         <v>6.8341499999999999E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>42917</v>
       </c>
@@ -11597,7 +12059,7 @@
         <v>4.4964964385206603</v>
       </c>
       <c r="R116">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.8211651808058882E-2</v>
       </c>
       <c r="S116">
@@ -11634,13 +12096,17 @@
         <v>-9.1182999999999998E-4</v>
       </c>
       <c r="AD116">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE116">
         <v>-4.9593700000000003E-3</v>
       </c>
-      <c r="AE116">
+      <c r="AF116">
         <v>7.795937E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>42948</v>
       </c>
@@ -11693,7 +12159,7 @@
         <v>4.4904095723672004</v>
       </c>
       <c r="R117">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.7930923851828204E-2</v>
       </c>
       <c r="S117">
@@ -11730,13 +12196,17 @@
         <v>1.36775E-3</v>
       </c>
       <c r="AD117">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE117">
         <v>-5.534762E-2</v>
       </c>
-      <c r="AE117">
+      <c r="AF117">
         <v>8.4347619999999998E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>42979</v>
       </c>
@@ -11789,7 +12259,7 @@
         <v>4.5021548705137002</v>
       </c>
       <c r="R118">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.8047534937920595E-2</v>
       </c>
       <c r="S118">
@@ -11826,13 +12296,17 @@
         <v>2.2795799999999998E-3</v>
       </c>
       <c r="AD118">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE118">
         <v>3.3382950000000002E-2</v>
       </c>
-      <c r="AE118">
+      <c r="AF118">
         <v>3.3617050000000002E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>43009</v>
       </c>
@@ -11885,7 +12359,7 @@
         <v>4.50741374422637</v>
       </c>
       <c r="R119">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.5720274931363676E-2</v>
       </c>
       <c r="S119">
@@ -11922,13 +12396,17 @@
         <v>-0.12910325</v>
       </c>
       <c r="AD119">
+        <f t="shared" si="3"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE119">
         <v>-4.6544130000000003E-2</v>
       </c>
-      <c r="AE119">
+      <c r="AF119">
         <v>-0.14245587000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>43040</v>
       </c>
@@ -11981,7 +12459,7 @@
         <v>4.5108183079753701</v>
       </c>
       <c r="R120">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.6193831256522451E-2</v>
       </c>
       <c r="S120">
@@ -12018,13 +12496,17 @@
         <v>-0.12910325</v>
       </c>
       <c r="AD120">
+        <f t="shared" si="3"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE120">
         <v>-5.5323200000000003E-3</v>
       </c>
-      <c r="AE120">
+      <c r="AF120">
         <v>-4.5467680000000003E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>43070</v>
       </c>
@@ -12077,7 +12559,7 @@
         <v>4.5439123792886296</v>
       </c>
       <c r="R121">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-3.6809760217636267E-2</v>
       </c>
       <c r="S121">
@@ -12114,13 +12596,17 @@
         <v>0</v>
       </c>
       <c r="AD121">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE121">
         <v>7.4612960000000006E-2</v>
       </c>
-      <c r="AE121">
+      <c r="AF121">
         <v>-4.8612959999999997E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>43101</v>
       </c>
@@ -12173,7 +12659,7 @@
         <v>4.5232470226757302</v>
       </c>
       <c r="R122">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.9387400820100744E-2</v>
       </c>
       <c r="S122">
@@ -12210,13 +12696,17 @@
         <v>2.2795799999999998E-3</v>
       </c>
       <c r="AD122">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE122">
         <v>2.0678209999999999E-2</v>
       </c>
-      <c r="AE122">
+      <c r="AF122">
         <v>-0.14867821000000001</v>
       </c>
     </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>43132</v>
       </c>
@@ -12269,7 +12759,7 @@
         <v>4.5241963195838499</v>
       </c>
       <c r="R123">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.0019661396401247E-2</v>
       </c>
       <c r="S123">
@@ -12306,13 +12796,17 @@
         <v>0</v>
       </c>
       <c r="AD123">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE123">
         <v>0</v>
       </c>
+      <c r="AF123">
+        <v>0</v>
+      </c>
     </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>43160</v>
       </c>
@@ -12365,7 +12859,7 @@
         <v>4.5340855705749101</v>
       </c>
       <c r="R124">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.0709851759545899E-2</v>
       </c>
       <c r="S124">
@@ -12402,13 +12896,17 @@
         <v>-9.1182999999999998E-4</v>
       </c>
       <c r="AD124">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE124">
         <v>-1.989235E-2</v>
       </c>
-      <c r="AE124">
+      <c r="AF124">
         <v>8.7892349999999994E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>43191</v>
       </c>
@@ -12461,7 +12959,7 @@
         <v>4.5392474972404999</v>
       </c>
       <c r="R125">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-4.9047145406288628E-2</v>
       </c>
       <c r="S125">
@@ -12498,13 +12996,17 @@
         <v>2.7355000000000001E-3</v>
       </c>
       <c r="AD125">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE125">
         <v>1.9643899999999999E-3</v>
       </c>
-      <c r="AE125">
+      <c r="AF125">
         <v>-7.96439E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>43221</v>
       </c>
@@ -12557,7 +13059,7 @@
         <v>4.5412191590330702</v>
       </c>
       <c r="R126">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.0235234345869628E-2</v>
       </c>
       <c r="S126">
@@ -12594,13 +13096,17 @@
         <v>0</v>
       </c>
       <c r="AD126">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE126">
         <v>0</v>
       </c>
+      <c r="AF126">
+        <v>0</v>
+      </c>
     </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>43252</v>
       </c>
@@ -12653,7 +13159,7 @@
         <v>4.5712323485309003</v>
       </c>
       <c r="R127">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-2.3529819622576831E-2</v>
       </c>
       <c r="S127">
@@ -12690,13 +13196,17 @@
         <v>-9.5742499999999994E-3</v>
       </c>
       <c r="AD127">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE127">
         <v>8.4851319999999994E-2</v>
       </c>
-      <c r="AE127">
+      <c r="AF127">
         <v>-8.9851319999999998E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>43282</v>
       </c>
@@ -12749,7 +13259,7 @@
         <v>4.5666236207458404</v>
       </c>
       <c r="R128">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-2.8848686660546186E-2</v>
       </c>
       <c r="S128">
@@ -12786,13 +13296,17 @@
         <v>-1.322158E-2</v>
       </c>
       <c r="AD128">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE128">
         <v>-6.7972290000000005E-2</v>
       </c>
-      <c r="AE128">
+      <c r="AF128">
         <v>6.7972290000000005E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>43313</v>
       </c>
@@ -12845,7 +13359,7 @@
         <v>4.5558084712056299</v>
       </c>
       <c r="R129">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-4.3014689110981941E-2</v>
       </c>
       <c r="S129">
@@ -12882,13 +13396,17 @@
         <v>0</v>
       </c>
       <c r="AD129">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE129">
         <v>0</v>
       </c>
+      <c r="AF129">
+        <v>0</v>
+      </c>
     </row>
-    <row r="130" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>43344</v>
       </c>
@@ -12941,7 +13459,7 @@
         <v>4.56034640861784</v>
       </c>
       <c r="R130">
-        <f t="shared" ref="R130:R193" si="2">Q130-G130</f>
+        <f t="shared" ref="R130:R193" si="4">Q130-G130</f>
         <v>-4.1603268762859358E-2</v>
       </c>
       <c r="S130">
@@ -12978,13 +13496,17 @@
         <v>0</v>
       </c>
       <c r="AD130">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE130">
         <v>-3.942826E-2</v>
       </c>
-      <c r="AE130">
+      <c r="AF130">
         <v>4.0428260000000001E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>43374</v>
       </c>
@@ -13037,7 +13559,7 @@
         <v>4.5699806779869503</v>
       </c>
       <c r="R131">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-3.602773990713537E-2</v>
       </c>
       <c r="S131">
@@ -13074,13 +13596,17 @@
         <v>0</v>
       </c>
       <c r="AD131">
+        <f t="shared" ref="AD131:AD194" si="5">AB131+AC131</f>
+        <v>0</v>
+      </c>
+      <c r="AE131">
         <v>2.8496750000000001E-2</v>
       </c>
-      <c r="AE131">
+      <c r="AF131">
         <v>-3.049675E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>43405</v>
       </c>
@@ -13133,7 +13659,7 @@
         <v>4.5731207652154398</v>
       </c>
       <c r="R132">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-3.6017023456119901E-2</v>
       </c>
       <c r="S132">
@@ -13170,13 +13696,17 @@
         <v>0</v>
       </c>
       <c r="AD132">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE132">
         <v>0</v>
       </c>
+      <c r="AF132">
+        <v>0</v>
+      </c>
     </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>43435</v>
       </c>
@@ -13229,7 +13759,7 @@
         <v>4.6099484382144604</v>
       </c>
       <c r="R133">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-2.0706409671067405E-3</v>
       </c>
       <c r="S133">
@@ -13266,13 +13796,17 @@
         <v>3.6473329999999998E-2</v>
       </c>
       <c r="AD133">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE133">
         <v>1.7447000000000001E-3</v>
       </c>
-      <c r="AE133">
+      <c r="AF133">
         <v>-1.7447000000000001E-3</v>
       </c>
     </row>
-    <row r="134" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>43466</v>
       </c>
@@ -13325,7 +13859,7 @@
         <v>4.6032398354091999</v>
       </c>
       <c r="R134">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-1.0366768957479344E-2</v>
       </c>
       <c r="S134">
@@ -13362,13 +13896,17 @@
         <v>6.3828299999999999E-3</v>
       </c>
       <c r="AD134">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE134">
         <v>-9.0203530000000004E-2</v>
       </c>
-      <c r="AE134">
+      <c r="AF134">
         <v>9.0203530000000004E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>43497</v>
       </c>
@@ -13421,7 +13959,7 @@
         <v>4.5714690914364802</v>
       </c>
       <c r="R135">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-4.2417699478774828E-2</v>
       </c>
       <c r="S135">
@@ -13458,13 +13996,17 @@
         <v>0</v>
       </c>
       <c r="AD135">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE135">
         <v>0</v>
       </c>
+      <c r="AF135">
+        <v>0</v>
+      </c>
     </row>
-    <row r="136" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>43525</v>
       </c>
@@ -13517,7 +14059,7 @@
         <v>4.5841232270499503</v>
       </c>
       <c r="R136">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-3.2324815760558678E-2</v>
       </c>
       <c r="S136">
@@ -13554,13 +14096,17 @@
         <v>-4.1032500000000001E-3</v>
       </c>
       <c r="AD136">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE136">
         <v>-5.315048E-2</v>
       </c>
-      <c r="AE136">
+      <c r="AF136">
         <v>5.4150480000000001E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>43556</v>
       </c>
@@ -13613,7 +14159,7 @@
         <v>4.5832760485643496</v>
       </c>
       <c r="R137">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-3.6905825954715255E-2</v>
       </c>
       <c r="S137">
@@ -13650,13 +14196,17 @@
         <v>5.9269199999999996E-3</v>
       </c>
       <c r="AD137">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE137">
         <v>4.0386079999999998E-2</v>
       </c>
-      <c r="AE137">
+      <c r="AF137">
         <v>-4.0386079999999998E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>43586</v>
       </c>
@@ -13709,7 +14259,7 @@
         <v>4.6009634455011703</v>
       </c>
       <c r="R138">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-2.3021704124806419E-2</v>
       </c>
       <c r="S138">
@@ -13746,13 +14296,17 @@
         <v>0</v>
       </c>
       <c r="AD138">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE138">
         <v>0</v>
       </c>
+      <c r="AF138">
+        <v>0</v>
+      </c>
     </row>
-    <row r="139" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>43617</v>
       </c>
@@ -13805,7 +14359,7 @@
         <v>4.60809207462533</v>
       </c>
       <c r="R139">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-2.0391105264602416E-2</v>
       </c>
       <c r="S139">
@@ -13842,13 +14396,17 @@
         <v>4.1032500000000001E-3</v>
       </c>
       <c r="AD139">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE139">
         <v>1.505486E-2</v>
       </c>
-      <c r="AE139">
+      <c r="AF139">
         <v>-1.105486E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>43647</v>
       </c>
@@ -13901,7 +14459,7 @@
         <v>4.6201619282733004</v>
       </c>
       <c r="R140">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-1.2555643949598405E-2</v>
       </c>
       <c r="S140">
@@ -13938,13 +14496,17 @@
         <v>0</v>
       </c>
       <c r="AD140">
-        <v>5.4999999999999997E-3</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="AE140">
         <v>5.4999999999999997E-3</v>
       </c>
+      <c r="AF140">
+        <v>5.4999999999999997E-3</v>
+      </c>
     </row>
-    <row r="141" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>43678</v>
       </c>
@@ -13997,7 +14559,7 @@
         <v>4.6030424444738598</v>
       </c>
       <c r="R141">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-3.2672032926418737E-2</v>
       </c>
       <c r="S141">
@@ -14034,13 +14596,17 @@
         <v>0</v>
       </c>
       <c r="AD141">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE141">
         <v>0</v>
       </c>
+      <c r="AF141">
+        <v>0</v>
+      </c>
     </row>
-    <row r="142" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>43709</v>
       </c>
@@ -14093,7 +14659,7 @@
         <v>4.6100960268015001</v>
       </c>
       <c r="R142">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-2.9228587539362749E-2</v>
       </c>
       <c r="S142">
@@ -14130,13 +14696,17 @@
         <v>4.5592000000000001E-4</v>
       </c>
       <c r="AD142">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE142">
         <v>3.2706390000000002E-2</v>
       </c>
-      <c r="AE142">
+      <c r="AF142">
         <v>-3.3706390000000003E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>43739</v>
       </c>
@@ -14189,7 +14759,7 @@
         <v>4.61753256588299</v>
       </c>
       <c r="R143">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-2.6329066173054194E-2</v>
       </c>
       <c r="S143">
@@ -14226,13 +14796,17 @@
         <v>5.790141E-2</v>
       </c>
       <c r="AD143">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE143">
         <v>-6.9324189999999994E-2</v>
       </c>
-      <c r="AE143">
+      <c r="AF143">
         <v>6.6324190000000005E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>43770</v>
       </c>
@@ -14285,7 +14859,7 @@
         <v>4.6138372731345898</v>
       </c>
       <c r="R144">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-3.3130687577492601E-2</v>
       </c>
       <c r="S144">
@@ -14322,13 +14896,17 @@
         <v>0</v>
       </c>
       <c r="AD144">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE144">
         <v>0</v>
       </c>
+      <c r="AF144">
+        <v>0</v>
+      </c>
     </row>
-    <row r="145" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>43800</v>
       </c>
@@ -14381,7 +14959,7 @@
         <v>4.6451159013123604</v>
       </c>
       <c r="R145">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-4.2234305253119331E-3</v>
       </c>
       <c r="S145">
@@ -14418,13 +14996,17 @@
         <v>4.695941E-2</v>
       </c>
       <c r="AD145">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE145">
         <v>-0.11714268</v>
       </c>
-      <c r="AE145">
+      <c r="AF145">
         <v>0.11714268</v>
       </c>
     </row>
-    <row r="146" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>43831</v>
       </c>
@@ -14477,7 +15059,7 @@
         <v>4.6542244828393704</v>
       </c>
       <c r="R146">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.0847907409918847E-3</v>
       </c>
       <c r="S146">
@@ -14514,13 +15096,17 @@
         <v>-8.6624200000000005E-3</v>
       </c>
       <c r="AD146">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE146">
         <v>-8.7590900000000006E-3</v>
       </c>
-      <c r="AE146">
+      <c r="AF146">
         <v>5.7590899999999997E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>43862</v>
       </c>
@@ -14573,7 +15159,7 @@
         <v>4.63500885615729</v>
       </c>
       <c r="R147">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-1.5322408231168261E-2</v>
       </c>
       <c r="S147">
@@ -14610,13 +15196,17 @@
         <v>0</v>
       </c>
       <c r="AD147">
-        <v>-5.0000000000000001E-4</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="AE147">
         <v>-5.0000000000000001E-4</v>
       </c>
+      <c r="AF147">
+        <v>-5.0000000000000001E-4</v>
+      </c>
     </row>
-    <row r="148" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>43891</v>
       </c>
@@ -14669,7 +15259,7 @@
         <v>4.6632030225989203</v>
       </c>
       <c r="R148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.0545045575600724E-3</v>
       </c>
       <c r="S148">
@@ -14706,13 +15296,17 @@
         <v>-0.12180858</v>
       </c>
       <c r="AD148">
+        <f t="shared" si="5"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE148">
         <v>8.9387330000000001E-2</v>
       </c>
-      <c r="AE148">
+      <c r="AF148">
         <v>-0.19238733</v>
       </c>
     </row>
-    <row r="149" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>43922</v>
       </c>
@@ -14765,7 +15359,7 @@
         <v>4.5752338708676801</v>
       </c>
       <c r="R149">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-7.9337327758827847E-2</v>
       </c>
       <c r="S149">
@@ -14802,13 +15396,17 @@
         <v>5.9269199999999996E-3</v>
       </c>
       <c r="AD149">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE149">
         <v>0.32310577000000001</v>
       </c>
-      <c r="AE149">
+      <c r="AF149">
         <v>-0.24610577</v>
       </c>
     </row>
-    <row r="150" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>43952</v>
       </c>
@@ -14861,7 +15459,7 @@
         <v>4.4982285653505896</v>
       </c>
       <c r="R150">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.15383340885923058</v>
       </c>
       <c r="S150">
@@ -14898,13 +15496,17 @@
         <v>3.16125E-3</v>
       </c>
       <c r="AD150">
+        <f t="shared" si="5"/>
+        <v>0.02</v>
+      </c>
+      <c r="AE150">
         <v>-0.16571865999999999</v>
       </c>
-      <c r="AE150">
+      <c r="AF150">
         <v>0.16871865999999999</v>
       </c>
     </row>
-    <row r="151" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>43983</v>
       </c>
@@ -14957,7 +15559,7 @@
         <v>4.5492051156056501</v>
       </c>
       <c r="R151">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.10108180422926694</v>
       </c>
       <c r="S151">
@@ -14994,13 +15596,17 @@
         <v>8.6382829999999994E-2</v>
       </c>
       <c r="AD151">
+        <f t="shared" si="5"/>
+        <v>0.15999999999999998</v>
+      </c>
+      <c r="AE151">
         <v>8.6361889999999997E-2</v>
       </c>
-      <c r="AE151">
+      <c r="AF151">
         <v>5.6638109999999998E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>44013</v>
       </c>
@@ -15053,7 +15659,7 @@
         <v>4.5935646401154102</v>
       </c>
       <c r="R152">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-5.8708276949066551E-2</v>
       </c>
       <c r="S152">
@@ -15090,13 +15696,17 @@
         <v>7.75058E-3</v>
       </c>
       <c r="AD152">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE152">
         <v>3.5540099999999998E-3</v>
       </c>
-      <c r="AE152">
+      <c r="AF152">
         <v>-1.555401E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>44044</v>
       </c>
@@ -15149,7 +15759,7 @@
         <v>4.5872324284839401</v>
       </c>
       <c r="R153">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-6.7053133293741851E-2</v>
       </c>
       <c r="S153">
@@ -15186,13 +15796,17 @@
         <v>4.5591700000000004E-3</v>
       </c>
       <c r="AD153">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE153">
         <v>-0.30433023999999997</v>
       </c>
-      <c r="AE153">
+      <c r="AF153">
         <v>0.25733023999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>44075</v>
       </c>
@@ -15245,7 +15859,7 @@
         <v>4.6133348071314701</v>
       </c>
       <c r="R154">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-4.5446738349108173E-2</v>
       </c>
       <c r="S154">
@@ -15282,13 +15896,17 @@
         <v>-5.1382829999999997E-2</v>
       </c>
       <c r="AD154">
+        <f t="shared" si="5"/>
+        <v>-0.09</v>
+      </c>
+      <c r="AE154">
         <v>-0.10400889000000001</v>
       </c>
-      <c r="AE154">
+      <c r="AF154">
         <v>-2.499111E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>44105</v>
       </c>
@@ -15341,7 +15959,7 @@
         <v>4.6487874816741996</v>
       </c>
       <c r="R155">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-1.2372264405762223E-2</v>
       </c>
       <c r="S155">
@@ -15378,13 +15996,17 @@
         <v>1.363225E-2</v>
       </c>
       <c r="AD155">
+        <f t="shared" si="5"/>
+        <v>0.03</v>
+      </c>
+      <c r="AE155">
         <v>-0.11012821</v>
       </c>
-      <c r="AE155">
+      <c r="AF155">
         <v>0.11312821000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>44136</v>
       </c>
@@ -15437,7 +16059,7 @@
         <v>4.6536274721424</v>
       </c>
       <c r="R156">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-8.1732282662985156E-3</v>
       </c>
       <c r="S156">
@@ -15474,13 +16096,17 @@
         <v>0</v>
       </c>
       <c r="AD156">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE156">
         <v>2.2930780000000001E-2</v>
       </c>
-      <c r="AE156">
+      <c r="AF156">
         <v>-2.893078E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>44166</v>
       </c>
@@ -15533,7 +16159,7 @@
         <v>4.6807148226719804</v>
       </c>
       <c r="R157">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5262826038174637E-2</v>
       </c>
       <c r="S157">
@@ -15570,13 +16196,17 @@
         <v>5.9269199999999996E-3</v>
       </c>
       <c r="AD157">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE157">
         <v>0.30440184999999997</v>
       </c>
-      <c r="AE157">
+      <c r="AF157">
         <v>-0.30740184999999998</v>
       </c>
     </row>
-    <row r="158" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>44197</v>
       </c>
@@ -15629,7 +16259,7 @@
         <v>4.6719068404662902</v>
       </c>
       <c r="R158">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.8688439810440372E-3</v>
       </c>
       <c r="S158">
@@ -15666,13 +16296,17 @@
         <v>4.5592000000000001E-4</v>
       </c>
       <c r="AD158">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE158">
         <v>-4.4879090000000003E-2</v>
       </c>
-      <c r="AE158">
+      <c r="AF158">
         <v>7.1879090000000007E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>44228</v>
       </c>
@@ -15725,7 +16359,7 @@
         <v>4.6595796183607501</v>
       </c>
       <c r="R159">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-6.2096444018893138E-3</v>
       </c>
       <c r="S159">
@@ -15762,13 +16396,17 @@
         <v>0</v>
       </c>
       <c r="AD159">
-        <v>-5.0000000000000001E-4</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="AE159">
         <v>-5.0000000000000001E-4</v>
       </c>
+      <c r="AF159">
+        <v>-5.0000000000000001E-4</v>
+      </c>
     </row>
-    <row r="160" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>44256</v>
       </c>
@@ -15821,7 +16459,7 @@
         <v>4.6822784592032702</v>
       </c>
       <c r="R160">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3219770224410787E-2</v>
       </c>
       <c r="S160">
@@ -15858,13 +16496,17 @@
         <v>6.3828299999999999E-3</v>
       </c>
       <c r="AD160">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE160">
         <v>-4.0229050000000002E-2</v>
       </c>
-      <c r="AE160">
+      <c r="AF160">
         <v>4.4229049999999999E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>44287</v>
       </c>
@@ -15917,7 +16559,7 @@
         <v>4.6771712292829504</v>
       </c>
       <c r="R161">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.3641170105696006E-3</v>
       </c>
       <c r="S161">
@@ -15954,13 +16596,17 @@
         <v>7.2946699999999996E-3</v>
       </c>
       <c r="AD161">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE161">
         <v>0.24447516</v>
       </c>
-      <c r="AE161">
+      <c r="AF161">
         <v>-0.23747515999999999</v>
       </c>
     </row>
-    <row r="162" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>44317</v>
       </c>
@@ -16013,7 +16659,7 @@
         <v>4.6748293094431999</v>
       </c>
       <c r="R162">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-9.6913685973367691E-3</v>
       </c>
       <c r="S162">
@@ -16050,13 +16696,17 @@
         <v>0</v>
       </c>
       <c r="AD162">
-        <v>-3.0000000000000001E-3</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="AE162">
         <v>-3.0000000000000001E-3</v>
       </c>
+      <c r="AF162">
+        <v>-3.0000000000000001E-3</v>
+      </c>
     </row>
-    <row r="163" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>44348</v>
       </c>
@@ -16109,7 +16759,7 @@
         <v>4.6991630069416699</v>
       </c>
       <c r="R163">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3213561066467427E-2</v>
       </c>
       <c r="S163">
@@ -16146,13 +16796,17 @@
         <v>4.1032500000000001E-3</v>
       </c>
       <c r="AD163">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE163">
         <v>7.8926109999999994E-2</v>
       </c>
-      <c r="AE163">
+      <c r="AF163">
         <v>-0.11292611</v>
       </c>
     </row>
-    <row r="164" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>44378</v>
       </c>
@@ -16205,7 +16859,7 @@
         <v>4.7122258672636299</v>
       </c>
       <c r="R164">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.0969562139880438E-2</v>
       </c>
       <c r="S164">
@@ -16242,13 +16896,17 @@
         <v>1.36775E-3</v>
       </c>
       <c r="AD164">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE164">
         <v>4.4455600000000003E-3</v>
       </c>
-      <c r="AE164">
+      <c r="AF164">
         <v>-5.4455600000000003E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>44409</v>
       </c>
@@ -16301,7 +16959,7 @@
         <v>4.7115308183279199</v>
       </c>
       <c r="R165">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3813477415171249E-2</v>
       </c>
       <c r="S165">
@@ -16338,13 +16996,17 @@
         <v>0</v>
       </c>
       <c r="AD165">
-        <v>-1.15E-2</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="AE165">
         <v>-1.15E-2</v>
       </c>
+      <c r="AF165">
+        <v>-1.15E-2</v>
+      </c>
     </row>
-    <row r="166" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>44440</v>
       </c>
@@ -16397,7 +17059,7 @@
         <v>4.71557698153938</v>
       </c>
       <c r="R166">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2673927040148136E-2</v>
       </c>
       <c r="S166">
@@ -16434,13 +17096,17 @@
         <v>-3.1763300000000002E-3</v>
       </c>
       <c r="AD166">
+        <f t="shared" si="5"/>
+        <v>-0.01</v>
+      </c>
+      <c r="AE166">
         <v>-9.4572119999999996E-2</v>
       </c>
-      <c r="AE166">
+      <c r="AF166">
         <v>1.157212E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>44470</v>
       </c>
@@ -16493,7 +17159,7 @@
         <v>4.7210531222126502</v>
       </c>
       <c r="R167">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4953557823494279E-2</v>
       </c>
       <c r="S167">
@@ -16530,13 +17196,17 @@
         <v>9.2294669999999995E-2</v>
       </c>
       <c r="AD167">
+        <f t="shared" si="5"/>
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="AE167">
         <v>6.0210050000000001E-2</v>
       </c>
-      <c r="AE167">
+      <c r="AF167">
         <v>1.5789950000000001E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>44501</v>
       </c>
@@ -16589,7 +17259,7 @@
         <v>4.7363056902184404</v>
       </c>
       <c r="R168">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3258632170693794E-2</v>
       </c>
       <c r="S168">
@@ -16626,13 +17296,17 @@
         <v>0</v>
       </c>
       <c r="AD168">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE168">
         <v>0</v>
       </c>
+      <c r="AF168">
+        <v>0</v>
+      </c>
     </row>
-    <row r="169" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>44531</v>
       </c>
@@ -16685,7 +17359,7 @@
         <v>4.7654970161080703</v>
       </c>
       <c r="R169">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.5262818001097216E-2</v>
       </c>
       <c r="S169">
@@ -16722,13 +17396,17 @@
         <v>4.1032500000000001E-3</v>
       </c>
       <c r="AD169">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE169">
         <v>2.4303060000000001E-2</v>
       </c>
-      <c r="AE169">
+      <c r="AF169">
         <v>-0.15330305999999999</v>
       </c>
     </row>
-    <row r="170" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>44562</v>
       </c>
@@ -16781,7 +17459,7 @@
         <v>4.7776199075323502</v>
       </c>
       <c r="R170">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.5494302134955866E-2</v>
       </c>
       <c r="S170">
@@ -16818,13 +17496,17 @@
         <v>0.12864733</v>
       </c>
       <c r="AD170">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="AE170">
         <v>2.622474E-2</v>
       </c>
-      <c r="AE170">
+      <c r="AF170">
         <v>0.10677526</v>
       </c>
     </row>
-    <row r="171" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>44593</v>
       </c>
@@ -16877,7 +17559,7 @@
         <v>4.7752745469184399</v>
       </c>
       <c r="R171">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.2552408060804616E-2</v>
       </c>
       <c r="S171">
@@ -16914,13 +17596,17 @@
         <v>0</v>
       </c>
       <c r="AD171">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE171">
         <v>0</v>
       </c>
+      <c r="AF171">
+        <v>0</v>
+      </c>
     </row>
-    <row r="172" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>44621</v>
       </c>
@@ -16973,7 +17659,7 @@
         <v>4.7926376068347896</v>
       </c>
       <c r="R172">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.1742492066856762E-2</v>
       </c>
       <c r="S172">
@@ -17010,13 +17696,17 @@
         <v>-0.26367750000000001</v>
       </c>
       <c r="AD172">
+        <f t="shared" si="5"/>
+        <v>-0.5</v>
+      </c>
+      <c r="AE172">
         <v>-0.29173496999999998</v>
       </c>
-      <c r="AE172">
+      <c r="AF172">
         <v>-0.17526502999999999</v>
       </c>
     </row>
-    <row r="173" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>44652</v>
       </c>
@@ -17069,7 +17759,7 @@
         <v>4.7939328323895003</v>
       </c>
       <c r="R173">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.1875076894546162E-2</v>
       </c>
       <c r="S173">
@@ -17106,13 +17796,17 @@
         <v>9.1183299999999991E-3</v>
       </c>
       <c r="AD173">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE173">
         <v>-0.1352621</v>
       </c>
-      <c r="AE173">
+      <c r="AF173">
         <v>8.9262099999999997E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>44682</v>
       </c>
@@ -17165,7 +17859,7 @@
         <v>4.8012199413939802</v>
       </c>
       <c r="R174">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.0018154400877961E-2</v>
       </c>
       <c r="S174">
@@ -17202,13 +17896,17 @@
         <v>0</v>
       </c>
       <c r="AD174">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE174">
         <v>0</v>
       </c>
+      <c r="AF174">
+        <v>0</v>
+      </c>
     </row>
-    <row r="175" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>44713</v>
       </c>
@@ -17261,7 +17959,7 @@
         <v>4.8221711232183999</v>
       </c>
       <c r="R175">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.3808662595597347E-2</v>
       </c>
       <c r="S175">
@@ -17298,13 +17996,17 @@
         <v>4.5592000000000001E-4</v>
       </c>
       <c r="AD175">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE175">
         <v>-0.22724796999999999</v>
       </c>
-      <c r="AE175">
+      <c r="AF175">
         <v>0.23024797</v>
       </c>
     </row>
-    <row r="176" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>44743</v>
       </c>
@@ -17357,7 +18059,7 @@
         <v>4.8302109686728398</v>
       </c>
       <c r="R176">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.1834298224986632E-2</v>
       </c>
       <c r="S176">
@@ -17394,13 +18096,17 @@
         <v>-2.7355000000000001E-3</v>
       </c>
       <c r="AD176">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE176">
         <v>0.17082194000000001</v>
       </c>
-      <c r="AE176">
+      <c r="AF176">
         <v>-0.15382193999999999</v>
       </c>
     </row>
-    <row r="177" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>44774</v>
       </c>
@@ -17453,7 +18159,7 @@
         <v>4.8142633850477701</v>
       </c>
       <c r="R177">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3650242610308894E-2</v>
       </c>
       <c r="S177">
@@ -17490,13 +18196,17 @@
         <v>0</v>
       </c>
       <c r="AD177">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE177">
         <v>0</v>
       </c>
+      <c r="AF177">
+        <v>0</v>
+      </c>
     </row>
-    <row r="178" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>44805</v>
       </c>
@@ -17549,7 +18259,7 @@
         <v>4.8137319606351596</v>
       </c>
       <c r="R178">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.4882189620161199E-3</v>
       </c>
       <c r="S178">
@@ -17586,13 +18296,17 @@
         <v>-0.25775058000000001</v>
       </c>
       <c r="AD178">
+        <f t="shared" si="5"/>
+        <v>-0.5</v>
+      </c>
+      <c r="AE178">
         <v>-0.11631753</v>
       </c>
-      <c r="AE178">
+      <c r="AF178">
         <v>-0.23268247</v>
       </c>
     </row>
-    <row r="179" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>44835</v>
       </c>
@@ -17645,7 +18359,7 @@
         <v>4.8234788576211898</v>
       </c>
       <c r="R179">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.0515189925314203E-3</v>
       </c>
       <c r="S179">
@@ -17682,13 +18396,17 @@
         <v>5.9269199999999996E-3</v>
       </c>
       <c r="AD179">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE179">
         <v>-9.2315430000000004E-2</v>
       </c>
-      <c r="AE179">
+      <c r="AF179">
         <v>7.6315430000000004E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>44866</v>
       </c>
@@ -17741,7 +18459,7 @@
         <v>4.8321429408145598</v>
       </c>
       <c r="R180">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.748521464922888E-4</v>
       </c>
       <c r="S180">
@@ -17778,13 +18496,17 @@
         <v>0</v>
       </c>
       <c r="AD180">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE180">
         <v>0</v>
       </c>
+      <c r="AF180">
+        <v>0</v>
+      </c>
     </row>
-    <row r="181" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>44896</v>
       </c>
@@ -17837,7 +18559,7 @@
         <v>4.8529654777659204</v>
       </c>
       <c r="R181">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.3802093722219482E-3</v>
       </c>
       <c r="S181">
@@ -17874,13 +18596,17 @@
         <v>0</v>
       </c>
       <c r="AD181">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE181">
         <v>7.2786879999999998E-2</v>
       </c>
-      <c r="AE181">
+      <c r="AF181">
         <v>0.12821312000000001</v>
       </c>
     </row>
-    <row r="182" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>44927</v>
       </c>
@@ -17933,7 +18659,7 @@
         <v>4.9116781873214501</v>
       </c>
       <c r="R182">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.5098910123933642E-2</v>
       </c>
       <c r="S182">
@@ -17970,13 +18696,17 @@
         <v>-0.11907308</v>
       </c>
       <c r="AD182">
+        <f t="shared" si="5"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE182">
         <v>8.0101829999999999E-2</v>
       </c>
-      <c r="AE182">
+      <c r="AF182">
         <v>2.8981699999999998E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>44958</v>
       </c>
@@ -18029,7 +18759,7 @@
         <v>4.9099951878673602</v>
       </c>
       <c r="R183">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.2594927792557691E-2</v>
       </c>
       <c r="S183">
@@ -18066,13 +18796,17 @@
         <v>0</v>
       </c>
       <c r="AD183">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE183">
         <v>0</v>
       </c>
+      <c r="AF183">
+        <v>0</v>
+      </c>
     </row>
-    <row r="184" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>44986</v>
       </c>
@@ -18125,7 +18859,7 @@
         <v>4.9187591491338596</v>
       </c>
       <c r="R184">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.2689268282063431E-2</v>
       </c>
       <c r="S184">
@@ -18162,13 +18896,17 @@
         <v>-3.1914199999999999E-3</v>
       </c>
       <c r="AD184">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE184">
         <v>-7.86549E-2</v>
       </c>
-      <c r="AE184">
+      <c r="AF184">
         <v>9.1654899999999997E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>45017</v>
       </c>
@@ -18221,7 +18959,7 @@
         <v>4.9166316423190404</v>
       </c>
       <c r="R185">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.4003540693680279E-2</v>
       </c>
       <c r="S185">
@@ -18258,13 +18996,17 @@
         <v>0.13229467</v>
       </c>
       <c r="AD185">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="AE185">
         <v>0.36911688999999998</v>
       </c>
-      <c r="AE185">
+      <c r="AF185">
         <v>-0.23611689</v>
       </c>
     </row>
-    <row r="186" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>45047</v>
       </c>
@@ -18317,7 +19059,7 @@
         <v>4.9196835477927401</v>
       </c>
       <c r="R186">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.1912159540786966E-2</v>
       </c>
       <c r="S186">
@@ -18354,13 +19096,17 @@
         <v>0</v>
       </c>
       <c r="AD186">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE186">
         <v>0</v>
       </c>
+      <c r="AF186">
+        <v>0</v>
+      </c>
     </row>
-    <row r="187" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>45078</v>
       </c>
@@ -18413,7 +19159,7 @@
         <v>4.9386785612847701</v>
       </c>
       <c r="R187">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.5853075135309673E-2</v>
       </c>
       <c r="S187">
@@ -18450,13 +19196,17 @@
         <v>7.2946699999999996E-3</v>
       </c>
       <c r="AD187">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE187">
         <v>-4.1612699999999999E-3</v>
       </c>
-      <c r="AE187">
+      <c r="AF187">
         <v>6.1612699999999999E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>45108</v>
       </c>
@@ -18509,7 +19259,7 @@
         <v>4.9403181255956499</v>
       </c>
       <c r="R188">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.049038213195999E-2</v>
       </c>
       <c r="S188">
@@ -18546,13 +19296,17 @@
         <v>3.1914199999999999E-3</v>
       </c>
       <c r="AD188">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE188">
         <v>-3.0805240000000001E-2</v>
       </c>
-      <c r="AE188">
+      <c r="AF188">
         <v>3.0805240000000001E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>45139</v>
       </c>
@@ -18605,7 +19359,7 @@
         <v>4.92127441558788</v>
       </c>
       <c r="R189">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2414688484447822E-2</v>
       </c>
       <c r="S189">
@@ -18642,13 +19396,17 @@
         <v>0</v>
       </c>
       <c r="AD189">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE189">
         <v>0</v>
       </c>
+      <c r="AF189">
+        <v>0</v>
+      </c>
     </row>
-    <row r="190" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>45170</v>
       </c>
@@ -18701,7 +19459,7 @@
         <v>4.9315865093660998</v>
       </c>
       <c r="R190">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6051852437992231E-2</v>
       </c>
       <c r="S190">
@@ -18738,13 +19496,17 @@
         <v>3.1914199999999999E-3</v>
       </c>
       <c r="AD190">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE190">
         <v>8.0192120000000006E-2</v>
       </c>
-      <c r="AE190">
+      <c r="AF190">
         <v>-6.9192119999999996E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>45200</v>
       </c>
@@ -18797,7 +19559,7 @@
         <v>4.94369705379005</v>
       </c>
       <c r="R191">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.2598665682704855E-2</v>
       </c>
       <c r="S191">
@@ -18834,13 +19596,17 @@
         <v>4.1032500000000001E-3</v>
       </c>
       <c r="AD191">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE191">
         <v>-2.4263900000000001E-3</v>
       </c>
-      <c r="AE191">
+      <c r="AF191">
         <v>1.42639E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>45231</v>
       </c>
@@ -18893,7 +19659,7 @@
         <v>4.9474812725190001</v>
       </c>
       <c r="R192">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9631507126112169E-2</v>
       </c>
       <c r="S192">
@@ -18930,13 +19696,17 @@
         <v>0</v>
       </c>
       <c r="AD192">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE192">
         <v>0</v>
       </c>
+      <c r="AF192">
+        <v>0</v>
+      </c>
     </row>
-    <row r="193" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>45261</v>
       </c>
@@ -18989,7 +19759,7 @@
         <v>4.9865449119496699</v>
       </c>
       <c r="R193">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.4200120956005016E-2</v>
       </c>
       <c r="S193">
@@ -19026,13 +19796,17 @@
         <v>1.36775E-3</v>
       </c>
       <c r="AD193">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE193">
         <v>-4.7931999999999998E-4</v>
       </c>
-      <c r="AE193">
+      <c r="AF193">
         <v>-9.952068E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>45292</v>
       </c>
@@ -19085,7 +19859,7 @@
         <v>5.0218004426478</v>
       </c>
       <c r="R194">
-        <f t="shared" ref="R194:R217" si="3">Q194-G194</f>
+        <f t="shared" ref="R194:R217" si="6">Q194-G194</f>
         <v>8.5003332119137021E-2</v>
       </c>
       <c r="S194">
@@ -19122,13 +19896,17 @@
         <v>0.1222645</v>
       </c>
       <c r="AD194">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="AE194">
         <v>8.3976200000000001E-2</v>
       </c>
-      <c r="AE194">
+      <c r="AF194">
         <v>9.9023799999999995E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>45323</v>
       </c>
@@ -19181,7 +19959,7 @@
         <v>5.01455476198156</v>
       </c>
       <c r="R195">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7.2636123970685418E-2</v>
       </c>
       <c r="S195">
@@ -19218,13 +19996,17 @@
         <v>0</v>
       </c>
       <c r="AD195">
+        <f t="shared" ref="AD195:AD211" si="7">AB195+AC195</f>
         <v>0</v>
       </c>
       <c r="AE195">
         <v>0</v>
       </c>
+      <c r="AF195">
+        <v>0</v>
+      </c>
     </row>
-    <row r="196" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>45352</v>
       </c>
@@ -19277,7 +20059,7 @@
         <v>5.0243258693525403</v>
       </c>
       <c r="R196">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7.7172644837872006E-2</v>
       </c>
       <c r="S196">
@@ -19314,13 +20096,17 @@
         <v>3.6473299999999998E-3</v>
       </c>
       <c r="AD196">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AE196">
         <v>6.6026009999999996E-2</v>
       </c>
-      <c r="AE196">
+      <c r="AF196">
         <v>-8.4026009999999998E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>45383</v>
       </c>
@@ -19373,7 +20159,7 @@
         <v>5.0267628839631797</v>
       </c>
       <c r="R197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7.4930400198793379E-2</v>
       </c>
       <c r="S197">
@@ -19410,13 +20196,17 @@
         <v>-1.36775E-3</v>
       </c>
       <c r="AD197">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AE197">
         <v>-0.14783793000000001</v>
       </c>
-      <c r="AE197">
+      <c r="AF197">
         <v>0.12583792999999999</v>
       </c>
     </row>
-    <row r="198" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>45413</v>
       </c>
@@ -19469,7 +20259,7 @@
         <v>5.0284026050886803</v>
       </c>
       <c r="R198">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7.15744642132492E-2</v>
       </c>
       <c r="S198">
@@ -19506,13 +20296,17 @@
         <v>0</v>
       </c>
       <c r="AD198">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE198">
         <v>0</v>
       </c>
+      <c r="AF198">
+        <v>0</v>
+      </c>
     </row>
-    <row r="199" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>45444</v>
       </c>
@@ -19565,7 +20359,7 @@
         <v>5.0458016584920102</v>
       </c>
       <c r="R199">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>8.3691851645759208E-2</v>
       </c>
       <c r="S199">
@@ -19602,13 +20396,17 @@
         <v>-5.6077740000000001E-2</v>
       </c>
       <c r="AD199">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AE199">
         <v>-3.1257899999999998E-3</v>
       </c>
-      <c r="AE199">
+      <c r="AF199">
         <v>3.112579E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>45474</v>
       </c>
@@ -19661,7 +20459,7 @@
         <v>5.0476870017812301</v>
       </c>
       <c r="R200">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>8.1558534804791805E-2</v>
       </c>
       <c r="S200">
@@ -19698,13 +20496,17 @@
         <v>-4.5592000000000001E-4</v>
       </c>
       <c r="AD200">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AE200">
         <v>3.1547520000000003E-2</v>
       </c>
-      <c r="AE200">
+      <c r="AF200">
         <v>-1.9547519999999999E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>45505</v>
       </c>
@@ -19757,7 +20559,7 @@
         <v>5.0378650042711097</v>
       </c>
       <c r="R201">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.9641542890912511E-2</v>
       </c>
       <c r="S201">
@@ -19794,13 +20596,17 @@
         <v>0</v>
       </c>
       <c r="AD201">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE201">
         <v>0</v>
       </c>
+      <c r="AF201">
+        <v>0</v>
+      </c>
     </row>
-    <row r="202" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>45536</v>
       </c>
@@ -19853,7 +20659,7 @@
         <v>5.0341945613284702</v>
       </c>
       <c r="R202">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.2180776495520007E-2</v>
       </c>
       <c r="S202">
@@ -19890,13 +20696,17 @@
         <v>4.5592000000000001E-4</v>
       </c>
       <c r="AD202">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AE202">
         <v>4.2006670000000003E-2</v>
       </c>
-      <c r="AE202">
+      <c r="AF202">
         <v>3.5993329999999997E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>45566</v>
       </c>
@@ -19949,7 +20759,7 @@
         <v>5.0366775533334396</v>
       </c>
       <c r="R203">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.2888393316576696E-2</v>
       </c>
       <c r="S203">
@@ -19986,13 +20796,17 @@
         <v>7.75058E-3</v>
       </c>
       <c r="AD203">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AE203">
         <v>4.497081E-2</v>
       </c>
-      <c r="AE203">
+      <c r="AF203">
         <v>-2.7970809999999999E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>45597</v>
       </c>
@@ -20045,7 +20859,7 @@
         <v>5.0407057774833701</v>
       </c>
       <c r="R204">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.2126509333850777E-2</v>
       </c>
       <c r="S204">
@@ -20082,13 +20896,17 @@
         <v>0</v>
       </c>
       <c r="AD204">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE204">
         <v>0</v>
       </c>
+      <c r="AF204">
+        <v>0</v>
+      </c>
     </row>
-    <row r="205" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>45627</v>
       </c>
@@ -20141,7 +20959,7 @@
         <v>5.0825726187538001</v>
       </c>
       <c r="R205">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>9.9497532569978731E-2</v>
       </c>
       <c r="S205">
@@ -20178,13 +20996,17 @@
         <v>0.17469491000000001</v>
       </c>
       <c r="AD205">
+        <f t="shared" si="7"/>
+        <v>0.25</v>
+      </c>
+      <c r="AE205">
         <v>-1.467862E-2</v>
       </c>
-      <c r="AE205">
+      <c r="AF205">
         <v>0.25167862000000002</v>
       </c>
     </row>
-    <row r="206" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>45658</v>
       </c>
@@ -20237,7 +21059,7 @@
         <v>5.09831573270327</v>
       </c>
       <c r="R206">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.11057189394811484</v>
       </c>
       <c r="S206">
@@ -20274,13 +21096,17 @@
         <v>0.12454408</v>
       </c>
       <c r="AD206">
+        <f t="shared" si="7"/>
+        <v>0.25</v>
+      </c>
+      <c r="AE206">
         <v>0.17011056999999999</v>
       </c>
-      <c r="AE206">
+      <c r="AF206">
         <v>-2.5110569999999999E-2</v>
       </c>
     </row>
-    <row r="207" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>45689</v>
       </c>
@@ -20333,7 +21159,7 @@
         <v>5.0912068400039301</v>
       </c>
       <c r="R207">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>9.7894744326234573E-2</v>
       </c>
       <c r="S207">
@@ -20370,13 +21196,17 @@
         <v>0</v>
       </c>
       <c r="AD207">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE207">
         <v>0</v>
       </c>
+      <c r="AF207">
+        <v>0</v>
+      </c>
     </row>
-    <row r="208" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>45717</v>
       </c>
@@ -20429,7 +21259,7 @@
         <v>5.0987914806023804</v>
       </c>
       <c r="R208">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.10200002940797415</v>
       </c>
       <c r="S208">
@@ -20466,13 +21296,17 @@
         <v>-4.5592000000000001E-4</v>
       </c>
       <c r="AD208">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AE208">
         <v>-0.12246003</v>
       </c>
-      <c r="AE208">
+      <c r="AF208">
         <v>0.12246003</v>
       </c>
     </row>
-    <row r="209" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>45748</v>
       </c>
@@ -20525,7 +21359,7 @@
         <v>5.1039824528979096</v>
       </c>
       <c r="R209">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.10188425616168928</v>
       </c>
       <c r="S209">
@@ -20562,13 +21396,17 @@
         <v>-0.10676334</v>
       </c>
       <c r="AD209">
+        <f t="shared" si="7"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AE209">
         <v>-0.15420149999999999</v>
       </c>
-      <c r="AE209">
+      <c r="AF209">
         <v>-9.5798499999999995E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>45778</v>
       </c>
@@ -20621,7 +21459,7 @@
         <v>5.1153615518450497</v>
       </c>
       <c r="R210">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.10927286583225726</v>
       </c>
       <c r="S210">
@@ -20658,13 +21496,17 @@
         <v>0</v>
       </c>
       <c r="AD210">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE210">
         <v>0</v>
       </c>
+      <c r="AF210">
+        <v>0</v>
+      </c>
     </row>
-    <row r="211" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>45809</v>
       </c>
@@ -20717,7 +21559,7 @@
         <v>5.1285097773356103</v>
       </c>
       <c r="R211">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.1192772692601638</v>
       </c>
       <c r="S211">
@@ -20754,13 +21596,17 @@
         <v>-4.5591700000000004E-3</v>
       </c>
       <c r="AD211">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AE211">
         <v>-3.3758299999999998E-2</v>
       </c>
-      <c r="AE211">
+      <c r="AF211">
         <v>3.3758299999999998E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>45839</v>
       </c>
@@ -20813,7 +21659,7 @@
         <v>5.1340710173106503</v>
       </c>
       <c r="R212">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.12012084734441064</v>
       </c>
       <c r="S212">
@@ -20835,7 +21681,7 @@
         <v>8.3042099457150851</v>
       </c>
     </row>
-    <row r="213" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>45870</v>
       </c>
@@ -20888,7 +21734,7 @@
         <v>5.11692595130061</v>
       </c>
       <c r="R213">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>9.9018969534554913E-2</v>
       </c>
       <c r="S213">
@@ -20910,7 +21756,7 @@
         <v>8.3058328478589267</v>
       </c>
     </row>
-    <row r="214" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>45901</v>
       </c>
@@ -20963,7 +21809,7 @@
         <v>5.1234123984926701</v>
       </c>
       <c r="R214">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.10089176194787974</v>
       </c>
       <c r="S214">
@@ -20985,7 +21831,7 @@
         <v>8.2744110593494771</v>
       </c>
     </row>
-    <row r="215" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>45931</v>
       </c>
@@ -21038,7 +21884,7 @@
         <v>5.12488287328887</v>
       </c>
       <c r="R215">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>9.7431271222575333E-2</v>
       </c>
       <c r="S215">
@@ -21060,7 +21906,7 @@
         <v>8.2630348243548255</v>
       </c>
     </row>
-    <row r="216" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>45962</v>
       </c>
@@ -21113,7 +21959,7 @@
         <v>5.1281589973024904</v>
       </c>
       <c r="R216">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>9.7878390898042511E-2</v>
       </c>
       <c r="S216">
@@ -21129,7 +21975,7 @@
         <v>14.3913303137755</v>
       </c>
     </row>
-    <row r="217" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>45992</v>
       </c>
@@ -21182,7 +22028,7 @@
         <v>5.1707632628214304</v>
       </c>
       <c r="R217">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.13790096189886114</v>
       </c>
       <c r="S217">
